--- a/reports/造化坊汇报说明书.xlsx
+++ b/reports/造化坊汇报说明书.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="394">
   <si>
     <t>🏭 造化坊 (Creation Forge)</t>
   </si>
   <si>
-    <t>汇报说明书 · 生成于 2026/7/21</t>
+    <t>汇报说明书 · 生成于 2026/7/23</t>
   </si>
   <si>
     <t>板块</t>
@@ -109,16 +109,70 @@
     <t>说明</t>
   </si>
   <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>工作日志</t>
+  </si>
+  <si>
+    <t>2026-07-22-开场黑幕UI制作.md</t>
+  </si>
+  <si>
+    <t>游戏界面制作工作流 — 梳理 UI 制作标准化流程，以开场黑幕为实战案例走通全流程</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-21-xiaohongshu-post13-14.md</t>
+  </si>
+  <si>
+    <t>小红书 2 期新帖 — 工作流管理 + 游戏图标管线转为图文帖子</t>
+  </si>
+  <si>
+    <t>2026-07-21-workflow-system.md</t>
+  </si>
+  <si>
+    <t>标准化工作流管理体系 — 双层结构（5 流程文档 + 3 SKILL），统一人机协作流程</t>
+  </si>
+  <si>
+    <t>2026-07-21-workflow-solidified.md</t>
+  </si>
+  <si>
+    <t>道具图标工作流固化 — 三个风格案例验证后，将流程固化为标准工作流文档</t>
+  </si>
+  <si>
+    <t>2026-07-21-workflow-maintenance.md</t>
+  </si>
+  <si>
+    <t>工作流文档维护 — 手动巡检更新多份文档，确认 SKILL 存放位置与共享局限性</t>
+  </si>
+  <si>
+    <t>2026-07-21-clash-royale-icons.md</t>
+  </si>
+  <si>
+    <t>皇室战争风格道具图标 — Supercell 3D cel-shaded + 三国题材融合</t>
+  </si>
+  <si>
+    <t>2026-07-21-asset-pipeline.md</t>
+  </si>
+  <si>
+    <t>Lovart + Photoshop 道具图标生产线 — 1024→256 二次元风格批量产出</t>
+  </si>
+  <si>
     <t>2026-07-20</t>
   </si>
   <si>
-    <t>工作日志</t>
+    <t>2026-07-20-xiaohongshu-restructure.md</t>
+  </si>
+  <si>
+    <t>小红书项目重构 — 目录扁平化（14 主题统一为日期-主题），Pixso 单文件导入</t>
   </si>
   <si>
     <t>2026-07-20-remove-preset-learning-path.md</t>
   </si>
   <si>
-    <t>去除预设三阶段学习路径 — 回归项目制学习本意，同步更新 6 份关联文档</t>
+    <t>去除预设三阶段学习路径 — 回归项目制学习本意</t>
   </si>
   <si>
     <t>2026-07-17</t>
@@ -127,19 +181,19 @@
     <t>2026-07-17-xiaohongshu-restructure.md</t>
   </si>
   <si>
-    <t>小红书项目 4 库结构重组 — 文案库/HTML库/Pixso截图/ + CLAUDE.md 行为规范</t>
+    <t>小红书项目 4 库结构重组 — 文案库/HTML库/Pixso截图/ + CLAUDE.md</t>
   </si>
   <si>
     <t>2026-07-17-xiaohongshu-post11-pixso-fix.md</t>
   </si>
   <si>
-    <t>post-11 产出 + Pixso 四问题修复 — 嵌套/命名/单图/对齐，确立 6+1 文件结构</t>
+    <t>post-11 产出 + Pixso 四问题修复 — 嵌套/命名/单图/对齐</t>
   </si>
   <si>
     <t>2026-07-17-game002-onboarding.md</t>
   </si>
   <si>
-    <t>GAME-002「开仙门」项目接入 — 35 脚本/4721 行/10 CSV，Godot 4.7 升级确认</t>
+    <t>GAME-002「开仙门」项目接入 — 35 脚本/4721 行/10 CSV，Godot 4.7</t>
   </si>
   <si>
     <t>2026-07-16</t>
@@ -325,16 +379,28 @@
     <t>每个问题都是一个交付</t>
   </si>
   <si>
-    <t>协作层</t>
-  </si>
-  <si>
-    <t>ai-collab/</t>
-  </si>
-  <si>
-    <t>决策记录/提示词库/复盘</t>
-  </si>
-  <si>
-    <t>AI 协作可追溯</t>
+    <t>工作流</t>
+  </si>
+  <si>
+    <t>docs/workflows/</t>
+  </si>
+  <si>
+    <t>标准化协作流程（双层：知识层+SKILL）</t>
+  </si>
+  <si>
+    <t>5 个流程 / 3 个 SKILL</t>
+  </si>
+  <si>
+    <t>知识库</t>
+  </si>
+  <si>
+    <t>docs/tool-guides/</t>
+  </si>
+  <si>
+    <t>工具软件知识库（Git/GitHub/Pixso）</t>
+  </si>
+  <si>
+    <t>介绍+操作+人机协作</t>
   </si>
   <si>
     <t>类别</t>
@@ -379,9 +445,6 @@
     <t>技术栈选型理由与版本</t>
   </si>
   <si>
-    <t>工作流</t>
-  </si>
-  <si>
     <t>03-workflow.md</t>
   </si>
   <si>
@@ -721,13 +784,13 @@
     <t>自媒体发布素材库</t>
   </si>
   <si>
-    <t>AI 记忆</t>
-  </si>
-  <si>
-    <t>j:\ceshi\ai-collab\</t>
-  </si>
-  <si>
-    <t>决策/提示词/复盘</t>
+    <t>工具知识库</t>
+  </si>
+  <si>
+    <t>j:\ceshi\docs\tool-guides\</t>
+  </si>
+  <si>
+    <t>Git/GitHub/Pixso 操作与人机协作</t>
   </si>
   <si>
     <t>汇报输出</t>
@@ -1823,7 +1886,7 @@
   <sheetPr>
     <tabColor rgb="FFE85D3A"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1919,128 +1982,240 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="D12" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>67</v>
+    <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2058,7 +2233,7 @@
   <sheetPr>
     <tabColor rgb="FF7B61FF"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2068,7 +2243,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2076,7 +2251,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2084,310 +2259,324 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+    <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>115</v>
+      <c r="B17" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>118</v>
+      <c r="A18" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>124</v>
+      <c r="B20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>127</v>
+      <c r="A21" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>130</v>
+      <c r="A22" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>133</v>
+      <c r="A23" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>136</v>
+      <c r="A24" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>139</v>
+      <c r="A25" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>143</v>
+      <c r="A26" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2416,7 +2605,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2424,7 +2613,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2432,223 +2621,223 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2677,7 +2866,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2685,7 +2874,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2693,13 +2882,13 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>28</v>
@@ -2707,128 +2896,128 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2836,80 +3025,80 @@
         <v>30</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
@@ -2917,114 +3106,114 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3053,7 +3242,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3061,7 +3250,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3072,38 +3261,38 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>14</v>
@@ -3111,13 +3300,13 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -3125,44 +3314,44 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3170,27 +3359,27 @@
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3198,167 +3387,167 @@
         <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3366,41 +3555,41 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3408,55 +3597,55 @@
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3464,181 +3653,181 @@
         <v>2</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/reports/造化坊汇报说明书.xlsx
+++ b/reports/造化坊汇报说明书.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="432">
   <si>
     <t>🏭 造化坊 (Creation Forge)</t>
   </si>
@@ -80,7 +80,7 @@
   </si>
   <si>
     <t xml:space="preserve">项目制学习 —— 不由课本决定学什么，由你选的项目决定。
-当前活跃项目：GAME-002 开仙门（Godot 4.7）+ 小红书自媒体内容线</t>
+活跃项目：GAME-002 开仙门（Godot 4.7）+ 小红书自媒体 + asset-pipeline 资产管线</t>
   </si>
   <si>
     <t>价值观</t>
@@ -109,16 +109,31 @@
     <t>说明</t>
   </si>
   <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>工作日志</t>
+  </si>
+  <si>
+    <t>2026-07-23-week1-retrospective.md</t>
+  </si>
+  <si>
+    <t>里程碑复盘 — 造化坊第一周（07-15 → 07-23）</t>
+  </si>
+  <si>
+    <t>2026-07-23-report-sync.md</t>
+  </si>
+  <si>
+    <t>汇报同步 + 工作流维护 + SKILL 体系讨论</t>
+  </si>
+  <si>
     <t>2026-07-22</t>
   </si>
   <si>
-    <t>工作日志</t>
-  </si>
-  <si>
     <t>2026-07-22-开场黑幕UI制作.md</t>
   </si>
   <si>
-    <t>游戏界面制作工作流 — 梳理 UI 制作标准化流程，以开场黑幕为实战案例走通全流程</t>
+    <t>游戏界面制作工作流梳理 + 开场黑幕 UI</t>
   </si>
   <si>
     <t>2026-07-21</t>
@@ -127,37 +142,37 @@
     <t>2026-07-21-xiaohongshu-post13-14.md</t>
   </si>
   <si>
-    <t>小红书 2 期新帖 — 工作流管理 + 游戏图标管线转为图文帖子</t>
+    <t>小红书 2 期新帖产出 + 流程优化</t>
   </si>
   <si>
     <t>2026-07-21-workflow-system.md</t>
   </si>
   <si>
-    <t>标准化工作流管理体系 — 双层结构（5 流程文档 + 3 SKILL），统一人机协作流程</t>
+    <t>标准化工作流管理体系建立</t>
   </si>
   <si>
     <t>2026-07-21-workflow-solidified.md</t>
   </si>
   <si>
-    <t>道具图标工作流固化 — 三个风格案例验证后，将流程固化为标准工作流文档</t>
+    <t>道具图标工作流固化</t>
   </si>
   <si>
     <t>2026-07-21-workflow-maintenance.md</t>
   </si>
   <si>
-    <t>工作流文档维护 — 手动巡检更新多份文档，确认 SKILL 存放位置与共享局限性</t>
+    <t>工作流文档维护 + asset-pipeline 新建</t>
   </si>
   <si>
     <t>2026-07-21-clash-royale-icons.md</t>
   </si>
   <si>
-    <t>皇室战争风格道具图标 — Supercell 3D cel-shaded + 三国题材融合</t>
+    <t>皇室战争风格道具图标生成</t>
   </si>
   <si>
     <t>2026-07-21-asset-pipeline.md</t>
   </si>
   <si>
-    <t>Lovart + Photoshop 道具图标生产线 — 1024→256 二次元风格批量产出</t>
+    <t>Lovart + Photoshop 游戏道具图标生产线</t>
   </si>
   <si>
     <t>2026-07-20</t>
@@ -166,13 +181,13 @@
     <t>2026-07-20-xiaohongshu-restructure.md</t>
   </si>
   <si>
-    <t>小红书项目重构 — 目录扁平化（14 主题统一为日期-主题），Pixso 单文件导入</t>
+    <t>小红书项目重构：目录统一 + 流程简化 + 补齐内容</t>
   </si>
   <si>
     <t>2026-07-20-remove-preset-learning-path.md</t>
   </si>
   <si>
-    <t>去除预设三阶段学习路径 — 回归项目制学习本意</t>
+    <t>去除预设学习路径，回归项目制学习本意</t>
   </si>
   <si>
     <t>2026-07-17</t>
@@ -181,19 +196,19 @@
     <t>2026-07-17-xiaohongshu-restructure.md</t>
   </si>
   <si>
-    <t>小红书项目 4 库结构重组 — 文案库/HTML库/Pixso截图/ + CLAUDE.md</t>
+    <t>小红书项目文件结构重组 + GAME-002 接入</t>
   </si>
   <si>
     <t>2026-07-17-xiaohongshu-post11-pixso-fix.md</t>
   </si>
   <si>
-    <t>post-11 产出 + Pixso 四问题修复 — 嵌套/命名/单图/对齐</t>
+    <t>小红书协作流程搭建 + post-11 产出 + Pixso 导入四问题修复</t>
   </si>
   <si>
     <t>2026-07-17-game002-onboarding.md</t>
   </si>
   <si>
-    <t>GAME-002「开仙门」项目接入 — 35 脚本/4721 行/10 CSV，Godot 4.7</t>
+    <t>GAME-002「开仙门」项目接入</t>
   </si>
   <si>
     <t>2026-07-16</t>
@@ -202,7 +217,7 @@
     <t>2026-07-16-pixso-layout.md</t>
   </si>
   <si>
-    <t>Pixso 排版设计 — v2 暗色模板 + MCP 协作指南 + 三轮设计迭代</t>
+    <t>Pixso MCP 接入 + 小红书帖子排版设计</t>
   </si>
   <si>
     <t>2026-07-15</t>
@@ -211,13 +226,13 @@
     <t>2026-07-15-first-xiaohongshu-post.md</t>
   </si>
   <si>
-    <t>第一篇小红书发布记录 — 造化坊理念首次对外传播</t>
+    <t>制作第一个小红书图文</t>
   </si>
   <si>
     <t>2026-07-15-ai-era-action.md</t>
   </si>
   <si>
-    <t>AI 时代行动方案 — 核心理念体系建设的执行计划</t>
+    <t>AI 时代如何躬身入局</t>
   </si>
   <si>
     <t>提交信息</t>
@@ -250,10 +265,34 @@
     <t>🟢 活跃开发中</t>
   </si>
   <si>
-    <t>Godot 4.x</t>
-  </si>
-  <si>
-    <t>修仙题材策略游戏。已建立完整协作体系（宪法/角色/5 阶段 SOP/质量体系/AI 记忆），游戏数据采用 CSV 驱动（card/enemy/form/peak/spirit/wave 等表）</t>
+    <t>Godot 4.7</t>
+  </si>
+  <si>
+    <t>修仙题材 Roguelike 塔防。V0.1 进度 11%，设计-代码断层，19 项待定决策。</t>
+  </si>
+  <si>
+    <t>小红书自媒体</t>
+  </si>
+  <si>
+    <t>🟢 内容持续产出</t>
+  </si>
+  <si>
+    <t>HTML/CSS + Pixso</t>
+  </si>
+  <si>
+    <t>AI 协作内容创作。14 期帖子（扁平目录），/new-post SKILL 自动化流程。</t>
+  </si>
+  <si>
+    <t>asset-pipeline</t>
+  </si>
+  <si>
+    <t>🟢 资产管线运行中</t>
+  </si>
+  <si>
+    <t>Lovart + Photoshop</t>
+  </si>
+  <si>
+    <t>游戏道具图标生产线。docs/scripts/outputs/templates 四层结构，3 个风格案例已验证。</t>
   </si>
   <si>
     <t>tutorial/01-hello-canvas</t>
@@ -265,327 +304,360 @@
     <t>Phaser 3.80+</t>
   </si>
   <si>
-    <t>Phaser 入门教程，了解项目结构和渲染循环</t>
+    <t>Phaser 入门教程，按需创建。</t>
   </si>
   <si>
     <t>核心理念体系</t>
   </si>
   <si>
+    <t>🟢 持续演进</t>
+  </si>
+  <si>
+    <t>文档</t>
+  </si>
+  <si>
+    <t>工作流管理体系（双层）+ 工具知识库 + SKILL 执行层。07-23 周度复盘：5 项改进全部落地。</t>
+  </si>
+  <si>
+    <t>🎨 设计体系</t>
+  </si>
+  <si>
+    <t>项目架构设计、协作体系设计、视觉设计</t>
+  </si>
+  <si>
+    <t>层级</t>
+  </si>
+  <si>
+    <t>组件</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>顶层配置</t>
+  </si>
+  <si>
+    <t>CLAUDE.md / settings.json</t>
+  </si>
+  <si>
+    <t>AI 行为规范 &amp; 项目配置</t>
+  </si>
+  <si>
+    <t>项目入口，控制 AI 协作行为</t>
+  </si>
+  <si>
+    <t>文档层</t>
+  </si>
+  <si>
+    <t>docs/zh-CN/</t>
+  </si>
+  <si>
+    <t>中文文档（宣言/技术栈/工作流/结构/规范/术语）</t>
+  </si>
+  <si>
+    <t>项目知识库主阵地</t>
+  </si>
+  <si>
+    <t>共享层</t>
+  </si>
+  <si>
+    <t>shared/types + shared/utils</t>
+  </si>
+  <si>
+    <t>跨项目复用的类型定义和工具函数</t>
+  </si>
+  <si>
+    <t>npm workspaces 子包</t>
+  </si>
+  <si>
+    <t>模板层</t>
+  </si>
+  <si>
+    <t>templates/game-phaser + game-godot</t>
+  </si>
+  <si>
+    <t>新项目快速启动模板</t>
+  </si>
+  <si>
+    <t>Vite + Phaser 或 Godot</t>
+  </si>
+  <si>
+    <t>项目层</t>
+  </si>
+  <si>
+    <t>projects/GAME-002 + xiaohongshu + asset-pipeline + tutorial + originals + sandbox</t>
+  </si>
+  <si>
+    <t>3 个活跃项目 + 教程/原创/实验</t>
+  </si>
+  <si>
+    <t>GAME-002 + 小红书 + asset-pipeline</t>
+  </si>
+  <si>
+    <t>工具层</t>
+  </si>
+  <si>
+    <t>tools/</t>
+  </si>
+  <si>
+    <t>脚手架、日志生成、报告生成等脚本</t>
+  </si>
+  <si>
+    <t>开发效率工具</t>
+  </si>
+  <si>
+    <t>工作层</t>
+  </si>
+  <si>
+    <t>works/</t>
+  </si>
+  <si>
+    <t>一事一记 + 视频草案</t>
+  </si>
+  <si>
+    <t>每个问题都是一个交付</t>
+  </si>
+  <si>
+    <t>工作流</t>
+  </si>
+  <si>
+    <t>docs/workflows/</t>
+  </si>
+  <si>
+    <t>标准化协作流程（双层：知识层+SKILL）</t>
+  </si>
+  <si>
+    <t>5 个流程 / 3 个 SKILL</t>
+  </si>
+  <si>
+    <t>知识库</t>
+  </si>
+  <si>
+    <t>docs/tool-guides/</t>
+  </si>
+  <si>
+    <t>工具软件知识库（Git/GitHub/Pixso）</t>
+  </si>
+  <si>
+    <t>介绍+操作+人机协作</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>路径</t>
+  </si>
+  <si>
+    <t>宣言</t>
+  </si>
+  <si>
+    <t>docs/zh-CN/manifesto.md</t>
+  </si>
+  <si>
+    <t>AI 时代新学习思想宣言</t>
+  </si>
+  <si>
+    <t>运转线路图</t>
+  </si>
+  <si>
+    <t>docs/zh-CN/operational-loop.md</t>
+  </si>
+  <si>
+    <t>日常循环：问题→解决→产出→记录→视频→发布</t>
+  </si>
+  <si>
+    <t>项目哲学</t>
+  </si>
+  <si>
+    <t>01-project-philosophy.md</t>
+  </si>
+  <si>
+    <t>项目制学习理念与论证</t>
+  </si>
+  <si>
+    <t>技术选型</t>
+  </si>
+  <si>
+    <t>02-tech-stack.md</t>
+  </si>
+  <si>
+    <t>技术栈选型理由与版本</t>
+  </si>
+  <si>
+    <t>03-workflow.md</t>
+  </si>
+  <si>
+    <t>开发工作流定义</t>
+  </si>
+  <si>
+    <t>项目结构</t>
+  </si>
+  <si>
+    <t>04-project-structure.md</t>
+  </si>
+  <si>
+    <t>目录结构与设计意图</t>
+  </si>
+  <si>
+    <t>编码规范</t>
+  </si>
+  <si>
+    <t>05-coding-standards.md</t>
+  </si>
+  <si>
+    <t>TypeScript/Phaser 编码规范</t>
+  </si>
+  <si>
+    <t>Git 规范</t>
+  </si>
+  <si>
+    <t>06-git-conventions.md</t>
+  </si>
+  <si>
+    <t>分支策略与提交规范</t>
+  </si>
+  <si>
+    <t>术语表</t>
+  </si>
+  <si>
+    <t>07-glossary.md</t>
+  </si>
+  <si>
+    <t>项目术语定义</t>
+  </si>
+  <si>
+    <t>用户手册</t>
+  </si>
+  <si>
+    <t>user-manual.md</t>
+  </si>
+  <si>
+    <t>新人上手操作指南</t>
+  </si>
+  <si>
+    <t>小红书</t>
+  </si>
+  <si>
+    <t>xiaohongshu-workflow.md</t>
+  </si>
+  <si>
+    <t>自媒体发布流程（已迁移至 workflows/）</t>
+  </si>
+  <si>
+    <t>工作流体系</t>
+  </si>
+  <si>
+    <t>docs/workflows/ (7 文档)</t>
+  </si>
+  <si>
+    <t>标准化协作流程：小红书/Pixso/Git/汇报/GAME002</t>
+  </si>
+  <si>
+    <t>SKILL 执行层</t>
+  </si>
+  <si>
+    <t>.claude/skills/ (3 SKILL)</t>
+  </si>
+  <si>
+    <t>.claude/skills/</t>
+  </si>
+  <si>
+    <t>可执行命令：/new-post /git-commit /sync-report</t>
+  </si>
+  <si>
+    <t>工具知识库</t>
+  </si>
+  <si>
+    <t>docs/tool-guides/ (7 文档)</t>
+  </si>
+  <si>
+    <t>Git/GitHub/Pixso 操作与人机协作</t>
+  </si>
+  <si>
+    <t>视觉设计</t>
+  </si>
+  <si>
+    <t>Pixso MCP</t>
+  </si>
+  <si>
+    <t>http://127.0.0.1:3667/mcp</t>
+  </si>
+  <si>
+    <t>连接 Pixso 设计工具</t>
+  </si>
+  <si>
+    <t>📋 任务看板</t>
+  </si>
+  <si>
+    <t>当前进行中和计划中的任务</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>✅ 已完成</t>
+  </si>
+  <si>
+    <t>创建宣言文档 (manifesto.md)</t>
+  </si>
+  <si>
+    <t>2026-07-15 完成</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>重构 README 和 CLAUDE.md</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>自媒体</t>
+  </si>
+  <si>
+    <t>创建小红书素材库 (post-01 ~ post-11)</t>
+  </si>
+  <si>
+    <t>2026-07-17 重组为 4 库结构</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>发布第一篇小红书笔记</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>项目初始化</t>
+  </si>
+  <si>
+    <t>2026-07-15 完成 (d4a599c)</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>去除预设学习路径，文档同步修正</t>
+  </si>
+  <si>
+    <t>2026-07-17：删除三阶段Phaser教程规划，学习由实际项目驱动</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>🟢 进行中</t>
   </si>
   <si>
-    <t>文档</t>
-  </si>
-  <si>
-    <t>完善 AI 时代新学习思想文档体系。截至 07-17：删除预设三阶段学习路径，学习内容由实际项目驱动。</t>
-  </si>
-  <si>
-    <t>🎨 设计体系</t>
-  </si>
-  <si>
-    <t>项目架构设计、协作体系设计、视觉设计</t>
-  </si>
-  <si>
-    <t>层级</t>
-  </si>
-  <si>
-    <t>组件</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>顶层配置</t>
-  </si>
-  <si>
-    <t>CLAUDE.md / settings.json</t>
-  </si>
-  <si>
-    <t>AI 行为规范 &amp; 项目配置</t>
-  </si>
-  <si>
-    <t>项目入口，控制 AI 协作行为</t>
-  </si>
-  <si>
-    <t>文档层</t>
-  </si>
-  <si>
-    <t>docs/zh-CN/</t>
-  </si>
-  <si>
-    <t>中文文档（宣言/技术栈/工作流/结构/规范/术语）</t>
-  </si>
-  <si>
-    <t>项目知识库主阵地</t>
-  </si>
-  <si>
-    <t>共享层</t>
-  </si>
-  <si>
-    <t>shared/types + shared/utils</t>
-  </si>
-  <si>
-    <t>跨项目复用的类型定义和工具函数</t>
-  </si>
-  <si>
-    <t>npm workspaces 子包</t>
-  </si>
-  <si>
-    <t>模板层</t>
-  </si>
-  <si>
-    <t>templates/game-phaser + game-godot</t>
-  </si>
-  <si>
-    <t>新项目快速启动模板</t>
-  </si>
-  <si>
-    <t>Vite + Phaser 或 Godot</t>
-  </si>
-  <si>
-    <t>项目层</t>
-  </si>
-  <si>
-    <t>projects/GAME-002 + xiaohongshu + tutorial + originals + sandbox</t>
-  </si>
-  <si>
-    <t>两个活跃项目 + 教程/原创/实验</t>
-  </si>
-  <si>
-    <t>GAME-002(Godot 4.7) + 小红书自媒体</t>
-  </si>
-  <si>
-    <t>工具层</t>
-  </si>
-  <si>
-    <t>tools/</t>
-  </si>
-  <si>
-    <t>脚手架、日志生成、报告生成等脚本</t>
-  </si>
-  <si>
-    <t>开发效率工具</t>
-  </si>
-  <si>
-    <t>工作层</t>
-  </si>
-  <si>
-    <t>works/</t>
-  </si>
-  <si>
-    <t>一事一记 + 视频草案</t>
-  </si>
-  <si>
-    <t>每个问题都是一个交付</t>
-  </si>
-  <si>
-    <t>工作流</t>
-  </si>
-  <si>
-    <t>docs/workflows/</t>
-  </si>
-  <si>
-    <t>标准化协作流程（双层：知识层+SKILL）</t>
-  </si>
-  <si>
-    <t>5 个流程 / 3 个 SKILL</t>
-  </si>
-  <si>
-    <t>知识库</t>
-  </si>
-  <si>
-    <t>docs/tool-guides/</t>
-  </si>
-  <si>
-    <t>工具软件知识库（Git/GitHub/Pixso）</t>
-  </si>
-  <si>
-    <t>介绍+操作+人机协作</t>
-  </si>
-  <si>
-    <t>类别</t>
-  </si>
-  <si>
-    <t>路径</t>
-  </si>
-  <si>
-    <t>宣言</t>
-  </si>
-  <si>
-    <t>docs/zh-CN/manifesto.md</t>
-  </si>
-  <si>
-    <t>AI 时代新学习思想宣言</t>
-  </si>
-  <si>
-    <t>运转线路图</t>
-  </si>
-  <si>
-    <t>docs/zh-CN/operational-loop.md</t>
-  </si>
-  <si>
-    <t>日常循环：问题→解决→产出→记录→视频→发布</t>
-  </si>
-  <si>
-    <t>项目哲学</t>
-  </si>
-  <si>
-    <t>01-project-philosophy.md</t>
-  </si>
-  <si>
-    <t>项目制学习理念与论证</t>
-  </si>
-  <si>
-    <t>技术选型</t>
-  </si>
-  <si>
-    <t>02-tech-stack.md</t>
-  </si>
-  <si>
-    <t>技术栈选型理由与版本</t>
-  </si>
-  <si>
-    <t>03-workflow.md</t>
-  </si>
-  <si>
-    <t>开发工作流定义</t>
-  </si>
-  <si>
-    <t>项目结构</t>
-  </si>
-  <si>
-    <t>04-project-structure.md</t>
-  </si>
-  <si>
-    <t>目录结构与设计意图</t>
-  </si>
-  <si>
-    <t>编码规范</t>
-  </si>
-  <si>
-    <t>05-coding-standards.md</t>
-  </si>
-  <si>
-    <t>TypeScript/Phaser 编码规范</t>
-  </si>
-  <si>
-    <t>Git 规范</t>
-  </si>
-  <si>
-    <t>06-git-conventions.md</t>
-  </si>
-  <si>
-    <t>分支策略与提交规范</t>
-  </si>
-  <si>
-    <t>术语表</t>
-  </si>
-  <si>
-    <t>07-glossary.md</t>
-  </si>
-  <si>
-    <t>项目术语定义</t>
-  </si>
-  <si>
-    <t>用户手册</t>
-  </si>
-  <si>
-    <t>user-manual.md</t>
-  </si>
-  <si>
-    <t>新人上手操作指南</t>
-  </si>
-  <si>
-    <t>小红书</t>
-  </si>
-  <si>
-    <t>xiaohongshu-workflow.md</t>
-  </si>
-  <si>
-    <t>自媒体发布流程</t>
-  </si>
-  <si>
-    <t>视觉设计</t>
-  </si>
-  <si>
-    <t>Pixso MCP</t>
-  </si>
-  <si>
-    <t>http://127.0.0.1:3667/mcp</t>
-  </si>
-  <si>
-    <t>连接 Pixso 设计工具</t>
-  </si>
-  <si>
-    <t>📋 任务看板</t>
-  </si>
-  <si>
-    <t>当前进行中和计划中的任务</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>任务</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>✅ 已完成</t>
-  </si>
-  <si>
-    <t>创建宣言文档 (manifesto.md)</t>
-  </si>
-  <si>
-    <t>2026-07-15 完成</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>重构 README 和 CLAUDE.md</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>自媒体</t>
-  </si>
-  <si>
-    <t>创建小红书素材库 (post-01 ~ post-11)</t>
-  </si>
-  <si>
-    <t>2026-07-17 重组为 4 库结构</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>发布第一篇小红书笔记</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>项目初始化</t>
-  </si>
-  <si>
-    <t>2026-07-15 完成 (d4a599c)</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>去除预设学习路径，文档同步修正</t>
-  </si>
-  <si>
-    <t>2026-07-17：删除三阶段Phaser教程规划，学习由实际项目驱动</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>GAME-002「开仙门」开发（Godot 4.7）</t>
   </si>
   <si>
@@ -646,7 +718,46 @@
     <t>建立汇报体系（本说明书）</t>
   </si>
   <si>
-    <t>定期更新此 Excel</t>
+    <t>07-23 周度复盘 + 5 项改进落地</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>工作流管理体系（双层结构）</t>
+  </si>
+  <si>
+    <t>docs/workflows/ (7 文档) + .claude/skills/ (3 SKILL)</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>docs/tool-guides/ (Git/GitHub/Pixso 共 7 文档)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>asset-pipeline 资产管线搭建</t>
+  </si>
+  <si>
+    <t>Lovart + Photoshop 道具图标生产线</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>基于 works/ 视频草案生产 (14 期存量)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>GAME-002 经营系统决策 (X1~X4)</t>
+  </si>
+  <si>
+    <t>阻塞 3 周，需用户逐项拍板</t>
   </si>
   <si>
     <t>🔗 项目地址 &amp; 资产地址</t>
@@ -679,7 +790,19 @@
     <t>j:\ceshi\projects\GAME-002\</t>
   </si>
   <si>
-    <t>Godot 修仙策略游戏</t>
+    <t>Godot 修仙 Roguelike 塔防</t>
+  </si>
+  <si>
+    <t>j:\ceshi\projects\xiaohongshu\</t>
+  </si>
+  <si>
+    <t>AI 协作内容创作</t>
+  </si>
+  <si>
+    <t>j:\ceshi\projects\asset-pipeline\</t>
+  </si>
+  <si>
+    <t>游戏道具图标资产管线</t>
   </si>
   <si>
     <t>教程项目</t>
@@ -778,21 +901,12 @@
     <t>projects/xiaohongshu/</t>
   </si>
   <si>
-    <t>j:\ceshi\projects\xiaohongshu\</t>
-  </si>
-  <si>
     <t>自媒体发布素材库</t>
   </si>
   <si>
-    <t>工具知识库</t>
-  </si>
-  <si>
     <t>j:\ceshi\docs\tool-guides\</t>
   </si>
   <si>
-    <t>Git/GitHub/Pixso 操作与人机协作</t>
-  </si>
-  <si>
     <t>汇报输出</t>
   </si>
   <si>
@@ -829,7 +943,7 @@
     <t>当前分支: main</t>
   </si>
   <si>
-    <t>11 期帖子 + 4 库结构 + CLAUDE.md 规范</t>
+    <t>14 期帖子 + 扁平目录 + /new-post SKILL</t>
   </si>
   <si>
     <t>包管理</t>
@@ -1886,7 +2000,7 @@
   <sheetPr>
     <tabColor rgb="FFE85D3A"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1940,21 +2054,21 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>30</v>
@@ -1968,63 +2082,63 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>30</v>
@@ -2038,7 +2152,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
@@ -2080,21 +2194,21 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>30</v>
@@ -2108,21 +2222,21 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>30</v>
@@ -2134,88 +2248,144 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="C24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="7" t="s">
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="B28" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>85</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2233,7 +2403,7 @@
   <sheetPr>
     <tabColor rgb="FF7B61FF"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2243,7 +2413,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2251,7 +2421,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2259,153 +2429,153 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>28</v>
@@ -2416,13 +2586,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2430,153 +2600,195 @@
         <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>164</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2594,7 +2806,7 @@
   <sheetPr>
     <tabColor rgb="FF4CAF50"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2605,7 +2817,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2613,7 +2825,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2621,223 +2833,308 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="C13" s="9" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>208</v>
+      <c r="A16" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -2855,7 +3152,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9800"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2866,7 +3163,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2874,7 +3171,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2882,13 +3179,13 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>28</v>
@@ -2896,324 +3193,352 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>225</v>
+        <v>87</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>239</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>112</v>
+        <v>278</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>30</v>
+        <v>281</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>116</v>
+        <v>282</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>117</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>98</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>253</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>256</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>259</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>158</v>
+        <v>301</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>73</v>
+        <v>308</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>280</v>
+        <v>78</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>286</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3567,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3250,7 +3575,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3261,38 +3586,38 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>14</v>
@@ -3300,13 +3625,13 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>14</v>
@@ -3314,44 +3639,44 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3359,27 +3684,27 @@
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3387,167 +3712,167 @@
         <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3555,41 +3880,41 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>349</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3597,55 +3922,55 @@
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3653,181 +3978,181 @@
         <v>2</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>374</v>
+        <v>412</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>382</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>385</v>
+        <v>423</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>387</v>
+        <v>425</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
